--- a/ig/mc-add-profils-dp/StructureDefinition-as-mailbox-mss.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-mailbox-mss.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-mailbox-mss.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil du type de données ContactPoint créé dans le cadre de l'Annuaire Santé pour décrire les boîtes aux lettres du service de messagerie sécurisée de santé (MSSanté) rattachées aux professionnels et aux structures.</t>
+    <t>Datatype profile créé à partir ContactPoint dans le cadre de l'Annuaire Santé pour décrire les boîtes aux lettres du service de messagerie sécurisée de santé (MSSanté) rattachées aux professionnels et aux structures.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-mailbox-mss.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
